--- a/daily_matches/job_matches_2026-09-21.xlsx
+++ b/daily_matches/job_matches_2026-09-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deepwatch</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,1267 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57420c889c62f95c</t>
+          <t>https://www.indeed.com/viewjob?jk=493232b0c9dbfe10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a469b8a7a12191d</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>West Lafayette, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd1170dc974ac6bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb519a1be92b285c</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54990a61c7da31dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=362682e4c4fa7950</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Xenon7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51ca424feb3d9362</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Data Engineering</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FourLeaf Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bethpage, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Cortex, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18438b84428c657e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aegis Mobile</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Columbia, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Azure ML, Synapse, Git, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cddb3162ff0a10d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior QA Engineer – Manual &amp; Automation Testing</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>9series</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, BigQuery, CI/CD, Jenkins, GitHub Actions, Git, BigQuery, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e8d391718153a38</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Synapse, Data Lake, Apache Airflow, Terraform, Snowflake, Databricks, Power BI, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8cef3fbaab3f7c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Production Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Webull Financial</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, MySQL, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bdbdd239109f14f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Copilot, S3, EC2, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, MongoDB, Python</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31a89b0de664aa93</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Quality Data</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Shure</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Niles, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f28540cb24e8a1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FourKites</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Kubernetes, AKS, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4653e5f13eb08312</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FourKites</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Kubernetes, AKS, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12d8aac2732a19c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FourKites</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Kubernetes, AKS, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6480dd4d711fa567</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Superior Automotive Group</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Tableau, Power BI, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b32326f024eeaf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Technical Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Visio Lending</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7cc262e2b6190c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>E T Consultant 1 – AI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>World Bank Group</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c0634552a472439</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Systems (Python)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Northbeam</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d925737c4ae9c18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Junior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Visto360 AI Inc.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cffb1289ad6c288b</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Visto360 AI Inc.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51cca9a7d53850c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Java/Python, SQL, Databricks</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Kafka, Tableau, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d42fb889c5ed759</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LexisNexis Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caa4730f4c49152e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LexisNexis Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=765ddd3a5310510b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IT LINK, LLC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=589c8654564f1b08</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7519f106646cfafb</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Senior Java Developer (SAP BTP/CAP)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>EPAM Systems</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D30" t="n">
         <v>11.1</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88d251cc0fd62f24</t>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=261609512021b9dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Quality Engineer II</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ICW Group</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb7787f754de32bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Account Executive, Commercial Acquisition</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58e77f647886b7dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Summer 2027 Undergraduate Internship - Software</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88e2bd8494f34c64</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Summer 2027 Undergraduate Internship - Software</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd0e590704088d5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Summer 2027 Undergraduate Internship - Software</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17a438b51b2a5131</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Salesforce AI Builder</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Everest Global Solutions</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff1d2dd15364e4b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Athena, Kubernetes, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e888510a4835b7b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Technologist</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b5bf456fcd19e5a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-21.xlsx
+++ b/daily_matches/job_matches_2026-09-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deepwatch</t>
+          <t>Labor Pharmacy Benefit Solutions, LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>West Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, CI/CD, GitHub Actions, Git, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493232b0c9dbfe10</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc0b811b718bd2a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, S3, EC2, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a469b8a7a12191d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd065039757b55c7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>West Lafayette, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1170dc974ac6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=94d4fb8c5ae21e05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Generative AI, RAG, S3, Glue, Synapse, Docker, Snowflake, PySpark, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb519a1be92b285c</t>
+          <t>https://www.indeed.com/viewjob?jk=9311b3d4d764c329</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr. Technical Implementations Specialist (US)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>MEASURED</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, S3, Redshift, BigQuery, AKS, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54990a61c7da31dd</t>
+          <t>https://www.indeed.com/viewjob?jk=323d447537a37a4d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>ShipStation Global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Gemini, BigQuery, CI/CD, Git, Databricks, BigQuery, PySpark, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362682e4c4fa7950</t>
+          <t>https://www.indeed.com/viewjob?jk=028e43335938f143</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Xenon7</t>
+          <t>ShipStation Global</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Gemini, BigQuery, CI/CD, Git, Databricks, BigQuery, PySpark, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ca424feb3d9362</t>
+          <t>https://www.indeed.com/viewjob?jk=5966248554dc0bb5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Engineering</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FourLeaf Federal Credit Union</t>
+          <t>Boats Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Cortex, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Athena, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18438b84428c657e</t>
+          <t>https://www.indeed.com/viewjob?jk=917ce891fbb59294</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aegis Mobile</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Azure ML, Synapse, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cddb3162ff0a10d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef57e790e48920b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior QA Engineer – Manual &amp; Automation Testing</t>
+          <t>Software Engineer III - DevOps AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9series</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, BigQuery, CI/CD, Jenkins, GitHub Actions, Git, BigQuery, MySQL, Python</t>
+          <t>RAG, Copilot, S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8d391718153a38</t>
+          <t>https://www.indeed.com/viewjob?jk=b781fa7970847c14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer IV (6329)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Synapse, Data Lake, Apache Airflow, Terraform, Snowflake, Databricks, Power BI, SQL</t>
+          <t>Generative AI, Prompt Engineering, BigQuery, CI/CD, Git, Snowflake, BigQuery, Kafka, Tableau, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cef3fbaab3f7c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e4007bc63b344853</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Software Engineer III- AI/ML Engineering, GPU ML Serving</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Webull Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MySQL, NoSQL, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Cassandra, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdbdd239109f14f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7241ef35d82f3a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Pj Dick-Trumbull-Lindy Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, MongoDB, Python</t>
+          <t>RAG, Dataflow, CI/CD, Git, PySpark, NoSQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a89b0de664aa93</t>
+          <t>https://www.indeed.com/viewjob?jk=e631e31ef8563e5c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer, Quality Data</t>
+          <t>Sr Systems Engineer I (DevOps, Agentic AI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shure</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f28540cb24e8a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e5ab74d9755093</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Innovation Associate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FourKites</t>
+          <t>Aculocity, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Kubernetes, AKS, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4653e5f13eb08312</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2bc0ebb77942f3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Innovation Associate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FourKites</t>
+          <t>Aculocity, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Kubernetes, AKS, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12d8aac2732a19c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5c48601cde6124f0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Innovation Associate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FourKites</t>
+          <t>Aculocity, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Kubernetes, AKS, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6480dd4d711fa567</t>
+          <t>https://www.indeed.com/viewjob?jk=9caa516a0c84aba6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AI Innovation Associate</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Superior Automotive Group</t>
+          <t>Aculocity, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Tableau, Power BI, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b32326f024eeaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=5950fe67cfeb896e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer</t>
+          <t>AI Innovation Associate</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visio Lending</t>
+          <t>Aculocity, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7cc262e2b6190c2</t>
+          <t>https://www.indeed.com/viewjob?jk=359e1cc43668f379</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E T Consultant 1 – AI Engineer</t>
+          <t>Full-Stack Engineer 4 (Golang, AWS)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, LLaMA, FastAPI, CI/CD, Git, Databricks, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0634552a472439</t>
+          <t>https://www.indeed.com/viewjob?jk=9769cef0a6e3ea3c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Systems (Python)</t>
+          <t>Software Developer in Test</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Northbeam</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d925737c4ae9c18</t>
+          <t>https://www.indeed.com/viewjob?jk=1d56dd2ecf0c554e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Junior AI Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Visto360 AI Inc.</t>
+          <t>Vikta Energy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, MLflow, AKS, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cffb1289ad6c288b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd65a32d3514dda8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Applied AI ML-Senior Associate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Visto360 AI Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cca9a7d53850c9</t>
+          <t>https://www.indeed.com/viewjob?jk=583221e583b610a2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III- Java/Python, SQL, Databricks</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Kafka, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d42fb889c5ed759</t>
+          <t>https://www.indeed.com/viewjob?jk=0f0875865ce1bf4f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Git, Kafka, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa4730f4c49152e</t>
+          <t>https://www.indeed.com/viewjob?jk=1617c0627135617f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Activated Insights</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>S3, Kubernetes, CI/CD, Snowflake, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=765ddd3a5310510b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d911c664f1ca9e3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IT LINK, LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, NoSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589c8654564f1b08</t>
+          <t>https://www.indeed.com/viewjob?jk=47adaf58d43cfa22</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7519f106646cfafb</t>
+          <t>https://www.indeed.com/viewjob?jk=cdbd08c1a411356f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Java Developer (SAP BTP/CAP)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261609512021b9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5c5c5749ef654f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Quality Engineer II</t>
+          <t>Software Engineer, On Device</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>KARMAN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1497,46 +1497,46 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Docker, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7787f754de32bf</t>
+          <t>https://www.indeed.com/viewjob?jk=57b267a54492a683</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Account Executive, Commercial Acquisition</t>
+          <t>Sr. Data Analyst, Customer Analytics (Insurance)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, Prompt Engineering, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e77f647886b7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbc8da113bedb88</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Summer 2027 Undergraduate Internship - Software</t>
+          <t>#Backend Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e2bd8494f34c64</t>
+          <t>https://www.indeed.com/viewjob?jk=684a35242f6696cc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Summer 2027 Undergraduate Internship - Software</t>
+          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e590704088d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d3630f2df8379b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Summer 2027 Undergraduate Internship - Software</t>
+          <t>Product Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>BWH HOTELS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, Terraform, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a438b51b2a5131</t>
+          <t>https://www.indeed.com/viewjob?jk=12fedf5444aebe03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Salesforce AI Builder</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Everest Global Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff1d2dd15364e4b1</t>
+          <t>https://www.indeed.com/viewjob?jk=24eb150e17e59711</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Athena, Kubernetes, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,42 +1721,707 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e888510a4835b7b5</t>
+          <t>https://www.indeed.com/viewjob?jk=546eca05acc376ae</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Technologist</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Phizenix</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=277bd887f83a6648</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Junior DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Phizenix</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b623db452a6662d</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Focused</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Git, Python, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b79aeaf4649d546</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Scientist Senior Associate — Business Observability &amp; AI Platform</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, AKS, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=698c72f406b4af33</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Database Administrator I</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Transcor Data Services</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83390bad559122e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator / Data Engineer - SQL Server</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Verizon</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Redshift, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50ec343ee8128a95</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator / Data Engineer - PostgreSQL / MySQL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Verizon</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Redshift, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5aa0925b726594a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Python OR Java Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=752aee13abd790ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Data and Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Databricks, PySpark, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12441236feddd585</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Joby Aviation</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>San Carlos, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00daa5209d1f9608</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Data Lake, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56ce877fa5577eab</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Specialist, Software Engineering</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetaNXT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D49" t="n">
         <v>10</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5bf456fcd19e5a</t>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4a59f62a067d38a</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nebraska Medicine</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AI Engineer, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22a6f85e52cd84dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Tax Digital Services Intern - AI Engineering - Summer 2027</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RSM</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Copilot, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2f818c29b54875c</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE) - Applied AI</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=442ba4528d843c3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>OneTrust</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03977e5c620ebcb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Science Senior Associate - Onboarding &amp; Engagement Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Cortex, Git, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=426ecc2419850bf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Red Platform</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RVO Health</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71d501dd84970151</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Red Platform</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RVO Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44e9c9f32cfe80dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Red Platform</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RVO Health</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4eab37744e4c07c6</t>
         </is>
       </c>
     </row>
